--- a/data/processed/IPC_limpio.xlsx
+++ b/data/processed/IPC_limpio.xlsx
@@ -23,7 +23,7 @@
     <t xml:space="preserve">ipc_lag_12</t>
   </si>
   <si>
-    <t xml:space="preserve">ipc_log_cambio</t>
+    <t xml:space="preserve">inflacion_anual</t>
   </si>
 </sst>
 </file>
